--- a/reports/excel-reports_cache_report:XII.xlsx
+++ b/reports/excel-reports_cache_report:XII.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>1830</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1072,7 +1072,7 @@
       </x:c>
       <x:c r="C17" s="12" t="s"/>
       <x:c r="D17" s="18" t="n">
-        <x:v>6780</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s"/>
       <x:c r="F17" s="1" t="s"/>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="C20" s="12" t="s"/>
       <x:c r="D20" s="17" t="n">
-        <x:v>3820</x:v>
+        <x:v>3940</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s"/>
       <x:c r="F20" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:XII.xlsx
+++ b/reports/excel-reports_cache_report:XII.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>1950</x:v>
+        <x:v>3420</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1072,7 +1072,7 @@
       </x:c>
       <x:c r="C17" s="12" t="s"/>
       <x:c r="D17" s="18" t="n">
-        <x:v>7500</x:v>
+        <x:v>13920</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s"/>
       <x:c r="F17" s="1" t="s"/>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="C20" s="12" t="s"/>
       <x:c r="D20" s="17" t="n">
-        <x:v>3940</x:v>
+        <x:v>6570</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>23580</x:v>
+        <x:v>35520</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>
@@ -1305,7 +1305,7 @@
       </x:c>
       <x:c r="C26" s="12" t="s"/>
       <x:c r="D26" s="8" t="n">
-        <x:v>300</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="E26" s="8" t="s"/>
       <x:c r="F26" s="1" t="s"/>
@@ -1332,7 +1332,7 @@
       </x:c>
       <x:c r="C27" s="12" t="s"/>
       <x:c r="D27" s="18" t="n">
-        <x:v>540</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E27" s="8" t="s"/>
       <x:c r="F27" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:XII.xlsx
+++ b/reports/excel-reports_cache_report:XII.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>3420</x:v>
+        <x:v>2670</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1072,7 +1072,7 @@
       </x:c>
       <x:c r="C17" s="12" t="s"/>
       <x:c r="D17" s="18" t="n">
-        <x:v>13920</x:v>
+        <x:v>11820</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s"/>
       <x:c r="F17" s="1" t="s"/>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="C20" s="12" t="s"/>
       <x:c r="D20" s="17" t="n">
-        <x:v>6570</x:v>
+        <x:v>3940</x:v>
       </x:c>
       <x:c r="E20" s="8" t="s"/>
       <x:c r="F20" s="1" t="s"/>
@@ -1178,7 +1178,7 @@
       </x:c>
       <x:c r="C21" s="12" t="s"/>
       <x:c r="D21" s="17" t="n">
-        <x:v>35520</x:v>
+        <x:v>23580</x:v>
       </x:c>
       <x:c r="E21" s="8" t="s"/>
       <x:c r="F21" s="1" t="s"/>
@@ -1305,7 +1305,7 @@
       </x:c>
       <x:c r="C26" s="12" t="s"/>
       <x:c r="D26" s="8" t="n">
-        <x:v>400</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E26" s="8" t="s"/>
       <x:c r="F26" s="1" t="s"/>
@@ -1332,7 +1332,7 @@
       </x:c>
       <x:c r="C27" s="12" t="s"/>
       <x:c r="D27" s="18" t="n">
-        <x:v>1000</x:v>
+        <x:v>1020</x:v>
       </x:c>
       <x:c r="E27" s="8" t="s"/>
       <x:c r="F27" s="1" t="s"/>

--- a/reports/excel-reports_cache_report:XII.xlsx
+++ b/reports/excel-reports_cache_report:XII.xlsx
@@ -968,7 +968,7 @@
       </x:c>
       <x:c r="C13" s="12" t="s"/>
       <x:c r="D13" s="8" t="n">
-        <x:v>2670</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s"/>
       <x:c r="F13" s="1" t="s"/>
@@ -1072,7 +1072,7 @@
       </x:c>
       <x:c r="C17" s="12" t="s"/>
       <x:c r="D17" s="18" t="n">
-        <x:v>11820</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="E17" s="8" t="s"/>
       <x:c r="F17" s="1" t="s"/>
@@ -1332,7 +1332,7 @@
       </x:c>
       <x:c r="C27" s="12" t="s"/>
       <x:c r="D27" s="18" t="n">
-        <x:v>1020</x:v>
+        <x:v>1040</x:v>
       </x:c>
       <x:c r="E27" s="8" t="s"/>
       <x:c r="F27" s="1" t="s"/>
